--- a/AAII_Financials/Quarterly/CVSA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CVSA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
   <si>
     <t>CVSA</t>
   </si>
@@ -656,161 +656,174 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>501400</v>
+      </c>
+      <c r="E8" s="3">
         <v>487000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>503400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>462300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>457100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>466100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>447700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>417400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>409900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>412700</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>216700</v>
+      </c>
+      <c r="E9" s="3">
         <v>210700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>205400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>200800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>198900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>199900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>186600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>186000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>182500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>175300</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>284600</v>
+      </c>
+      <c r="E10" s="3">
         <v>276300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>298000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>261500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>258200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>266200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>261100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>231400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>227400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>237300</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -823,8 +836,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -855,8 +869,11 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,72 +904,81 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E14" s="3">
         <v>1100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3900</v>
-      </c>
-      <c r="F14" s="3">
-        <v>-400</v>
       </c>
       <c r="G14" s="3">
         <v>-400</v>
       </c>
       <c r="H14" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I14" s="3">
         <v>7100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-5100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E15" s="3">
         <v>14200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>13800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>13100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>13200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>13100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>13000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>12600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>17100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>18800</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -962,72 +988,79 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>404800</v>
+      </c>
+      <c r="E17" s="3">
         <v>394800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>388200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>376500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>379800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>368600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>349100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>345100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>337100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>332000</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>96500</v>
+      </c>
+      <c r="E18" s="3">
         <v>92200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>115200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>85800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>77300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>97500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>98600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>72300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>72800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>80600</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1040,8 +1073,9 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1072,136 +1106,151 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>110600</v>
+      </c>
+      <c r="E21" s="3">
         <v>106400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>128900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>98900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>90600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>110500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>111600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>84900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>89900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>99400</v>
       </c>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E22" s="3">
         <v>13600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>10900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>11100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>10900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>13100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>13900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>14500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>88400</v>
+      </c>
+      <c r="E23" s="3">
         <v>77900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>101900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>76900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>68600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>79300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>92200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>58400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>55700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>48000</v>
       </c>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E24" s="3">
         <v>20000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>25800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>15800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>14100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>18500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>22600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>12200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1232,72 +1281,81 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>72200</v>
+      </c>
+      <c r="E26" s="3">
         <v>58000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>76100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>61100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>54500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>60800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>69600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>46200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>50600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>37400</v>
       </c>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>71700</v>
+      </c>
+      <c r="E27" s="3">
         <v>41600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>76400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>61800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>54200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>60800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>75900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>46200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>49400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>36800</v>
       </c>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1328,40 +1386,46 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E29" s="3">
         <v>-16300</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>300</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>800</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-300</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>6300</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-1200</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1392,8 +1456,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1424,8 +1491,11 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1456,40 +1526,46 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>71700</v>
+      </c>
+      <c r="E33" s="3">
         <v>41600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>76400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>61800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>54200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>60800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>75900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>46200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>49400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>36800</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1520,77 +1596,86 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>71700</v>
+      </c>
+      <c r="E35" s="3">
         <v>41600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>76400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>61800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>54200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>60800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>75900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>46200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>49400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>36800</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1603,8 +1688,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1617,40 +1703,44 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>406300</v>
+      </c>
+      <c r="E41" s="3">
         <v>147000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>56300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>264700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>199600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>219000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>194000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>264800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>219300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>179800</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1681,40 +1771,46 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>169600</v>
+      </c>
+      <c r="E43" s="3">
         <v>175900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>162800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>194800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>146200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>163000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>147000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>171500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>126800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>140900</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1745,72 +1841,81 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E45" s="3">
         <v>14100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>12900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>652400</v>
+      </c>
+      <c r="E46" s="3">
         <v>403800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>303000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>567200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>416200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>450300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>407100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>516900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>418100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>387600</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1841,72 +1946,81 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>507000</v>
+      </c>
+      <c r="E48" s="3">
         <v>478100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>455500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>447100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>447300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>449200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>434700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>416400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>425300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>442300</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1715500</v>
+      </c>
+      <c r="E49" s="3">
         <v>1718300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1721100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1723900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1726700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1729500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1732300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1735200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1738000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1745300</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1937,8 +2051,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1969,40 +2086,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>101500</v>
+      </c>
+      <c r="E52" s="3">
         <v>99900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>103000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>100300</v>
       </c>
-      <c r="G52" s="3">
-        <v>64500</v>
-      </c>
       <c r="H52" s="3">
+        <v>96900</v>
+      </c>
+      <c r="I52" s="3">
         <v>103700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>85000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>87400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>84900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>48800</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2033,40 +2156,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3012700</v>
+      </c>
+      <c r="E54" s="3">
         <v>2737400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2614700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2867500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2752400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2789800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2723000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2817700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2741400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2715000</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2079,8 +2208,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2093,200 +2223,219 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>124800</v>
+      </c>
+      <c r="E57" s="3">
         <v>97300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>103100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>104600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>105000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>98700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>66900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>91400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>102600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>92200</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E58" s="3">
         <v>39100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>33900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>34400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>35200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>34900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>32600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>32300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>31400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>32500</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>260600</v>
+      </c>
+      <c r="E59" s="3">
         <v>277100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>181400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>322900</v>
       </c>
-      <c r="G59" s="3">
-        <v>242600</v>
-      </c>
       <c r="H59" s="3">
+        <v>214100</v>
+      </c>
+      <c r="I59" s="3">
         <v>248000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>201000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>320000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>185300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>231100</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>596800</v>
+      </c>
+      <c r="E60" s="3">
         <v>580400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>442900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>576600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>507900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>540600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>384600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>551300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>487700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>509100</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>865600</v>
+      </c>
+      <c r="E61" s="3">
         <v>697200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>695600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>741600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>738800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>745600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>832000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>811100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>816400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>807800</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E62" s="3">
         <v>7600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>12800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>38400</v>
       </c>
-      <c r="G62" s="3">
-        <v>40100</v>
-      </c>
       <c r="H62" s="3">
+        <v>15100</v>
+      </c>
+      <c r="I62" s="3">
         <v>14100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>19100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>25600</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2317,8 +2466,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2349,8 +2501,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2381,40 +2536,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1566500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1373300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1235900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1409800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1318700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1357000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1284000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1427800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1372300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1394100</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2427,8 +2588,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2459,8 +2621,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2491,8 +2656,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2523,8 +2691,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2555,40 +2726,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3029100</v>
+      </c>
+      <c r="E72" s="3">
         <v>2957400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2915800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2839400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2777600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2723400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2662500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2586700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2540500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2491100</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2619,8 +2796,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2651,8 +2831,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2683,40 +2866,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1446200</v>
+      </c>
+      <c r="E76" s="3">
         <v>1364100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1378800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1457600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1433600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1432700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1438900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1390000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1369100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1321000</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2747,77 +2936,86 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>71700</v>
+      </c>
+      <c r="E81" s="3">
         <v>41600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>76400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>61800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>54200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>60800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>75900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>46200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>49400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>36800</v>
       </c>
     </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2830,40 +3028,44 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E83" s="3">
         <v>21500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>17300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>16800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>17700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>17900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>18600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>18100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>20300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>19500</v>
       </c>
     </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2894,8 +3096,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2926,8 +3131,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2958,8 +3166,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2990,8 +3201,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3022,40 +3236,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E89" s="3">
         <v>186200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>29700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>130500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>59700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>207900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-19000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>89300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>60300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>153600</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3068,40 +3288,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-26800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-20200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-14600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-16000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-19000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-10200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-16600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12700</v>
       </c>
     </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3132,8 +3356,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3164,40 +3391,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-20200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-19600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-16000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-15700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12700</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3210,8 +3443,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3242,8 +3476,11 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3274,8 +3511,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3306,8 +3546,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3338,40 +3581,46 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>162800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-75700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-217700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-49500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-68100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-172100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-41800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-34100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-10700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-139700</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3402,36 +3651,42 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>258900</v>
+      </c>
+      <c r="E102" s="3">
         <v>90200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-207500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>65000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-20000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>25800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-71500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>45700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>33900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1200</v>
       </c>
     </row>
